--- a/data/trans_dic/P2A_ner_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,8</t>
+          <t>0,59; 5,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,25</t>
+          <t>0,91; 7,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 10,07</t>
+          <t>2,17; 9,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,05</t>
+          <t>2,32; 8,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,0</t>
+          <t>1,18; 6,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,94</t>
+          <t>0,62; 5,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,62</t>
+          <t>1,41; 7,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 7,24</t>
+          <t>1,5; 6,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,19</t>
+          <t>1,22; 5,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,45</t>
+          <t>1,18; 5,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,36</t>
+          <t>2,53; 7,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,34</t>
+          <t>2,26; 6,48</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,59</t>
+          <t>0,98; 5,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,95</t>
+          <t>0,48; 4,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 7,7</t>
+          <t>2,28; 7,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 7,11</t>
+          <t>2,33; 7,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,54</t>
+          <t>0,48; 4,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,09</t>
+          <t>2,68; 8,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,29</t>
+          <t>3,34; 8,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,1</t>
+          <t>1,16; 4,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,05</t>
+          <t>0,23; 2,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,72</t>
+          <t>2,97; 6,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,38</t>
+          <t>3,5; 7,16</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,22</t>
+          <t>0,57; 5,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,36</t>
+          <t>1,04; 6,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 10,88</t>
+          <t>3,45; 10,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,74</t>
+          <t>2,52; 8,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,27</t>
+          <t>2,08; 8,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,09</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,62</t>
+          <t>1,86; 7,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 10,76</t>
+          <t>4,08; 10,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,56</t>
+          <t>1,81; 5,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,98</t>
+          <t>0,98; 4,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,68</t>
+          <t>3,19; 7,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,31</t>
+          <t>3,92; 8,73</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,16</t>
+          <t>0,44; 4,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,74</t>
+          <t>1,99; 7,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,62</t>
+          <t>2,31; 7,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 11,67</t>
+          <t>4,47; 11,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,78</t>
+          <t>0,83; 4,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,76</t>
+          <t>0,41; 3,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 9,46</t>
+          <t>3,15; 9,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 11,14</t>
+          <t>3,75; 11,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,5</t>
+          <t>1,0; 3,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,73</t>
+          <t>1,47; 4,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,87</t>
+          <t>3,22; 7,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 10,24</t>
+          <t>4,98; 10,18</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,38</t>
+          <t>1,35; 3,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,54</t>
+          <t>1,89; 4,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,75</t>
+          <t>3,57; 6,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,06</t>
+          <t>4,05; 7,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,11</t>
+          <t>1,7; 4,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,39</t>
+          <t>0,75; 2,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,42</t>
+          <t>3,42; 6,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,53</t>
+          <t>4,34; 7,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,31</t>
+          <t>1,74; 3,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,05</t>
+          <t>1,44; 2,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,05</t>
+          <t>3,9; 6,01</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,6; 6,74</t>
+          <t>4,58; 6,69</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2443</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4625</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5548</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3743</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2868</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3985</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4798</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>6186</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6095</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8609</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>10347</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>617; 5564</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>882; 7615</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1951; 8911</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2718; 10128</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1394; 8179</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>702; 6539</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1475; 8353</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2105; 9738</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2721; 11643</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2468; 11483</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4928; 14700</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5829; 16710</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1923</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6574</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8314</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2597</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8599</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>14208</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5779</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2570</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>15173</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>22522</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1229; 6998</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>622; 5187</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3458; 11103</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4437; 14429</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>679; 6458</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3251</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4703; 14586</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>8516; 21645</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3069; 10924</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>643; 6417</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>9722; 22240</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>15588; 31891</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2465</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3053</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7616</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9834</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5423</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>12336</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4803</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13039</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>22169</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>619; 5452</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1089; 6581</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4018; 12190</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4798; 16476</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2345; 9248</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4476</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2465; 10082</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>7564; 20028</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3999; 12268</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2173; 9023</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>7955; 19376</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>14733; 32796</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2910</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5982</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12366</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9080</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>12513</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6280</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>8117</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>16554</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>24879</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>720; 6925</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2906; 10474</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3858; 12649</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7506; 18831</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1302; 7419</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>642; 5880</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4977; 15358</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>6796; 20920</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3239; 11773</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>4431; 14015</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>10463; 24825</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>17376; 35538</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14185</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>26289</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>36062</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>43855</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>25448</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>21585</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>53375</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>79916</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>6795; 17334</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9022; 21847</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18735; 35273</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>26948; 46707</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8985; 21348</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4017; 13079</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>19518; 36715</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>33070; 55711</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>17985; 34398</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>14645; 30019</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>42709; 65880</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>65472; 95484</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_ner_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,29</t>
+          <t>0,58; 5,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,84</t>
+          <t>0,77; 7,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 9,89</t>
+          <t>2,18; 10,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,64</t>
+          <t>2,28; 8,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,91</t>
+          <t>1,21; 6,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,81</t>
+          <t>0,74; 6,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,98</t>
+          <t>1,44; 8,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,94</t>
+          <t>1,41; 6,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,21</t>
+          <t>1,31; 4,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 5,48</t>
+          <t>1,42; 5,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,55</t>
+          <t>2,48; 7,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,48</t>
+          <t>2,34; 6,78</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,6</t>
+          <t>0,99; 5,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,52 +867,52 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,31</t>
+          <t>2,01; 7,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,57</t>
+          <t>2,39; 7,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,59</t>
+          <t>0,44; 4,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 8,32</t>
+          <t>2,72; 7,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,49</t>
+          <t>3,4; 8,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,11</t>
+          <t>0,96; 4,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,26</t>
+          <t>0,23; 2,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,8</t>
+          <t>3,05; 6,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,16</t>
+          <t>3,46; 7,14</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,06</t>
+          <t>0,59; 5,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,28</t>
+          <t>1,06; 6,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 10,46</t>
+          <t>3,61; 10,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,65</t>
+          <t>2,45; 8,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,22</t>
+          <t>2,06; 8,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,37; 4,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,59</t>
+          <t>1,96; 8,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 10,81</t>
+          <t>4,0; 10,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,57</t>
+          <t>1,66; 5,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,07</t>
+          <t>0,98; 4,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,77</t>
+          <t>3,27; 7,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 8,73</t>
+          <t>3,95; 8,25</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,19</t>
+          <t>0,52; 4,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,17</t>
+          <t>1,99; 7,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 7,58</t>
+          <t>2,08; 7,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,21</t>
+          <t>4,23; 11,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,73</t>
+          <t>0,85; 5,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,79</t>
+          <t>0,42; 3,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 9,71</t>
+          <t>3,1; 9,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,75; 11,54</t>
+          <t>3,92; 11,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,65</t>
+          <t>1,02; 3,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,66</t>
+          <t>1,43; 4,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,64</t>
+          <t>3,17; 7,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,18</t>
+          <t>4,99; 9,89</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,44</t>
+          <t>1,25; 3,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,58</t>
+          <t>1,84; 4,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,71</t>
+          <t>3,72; 6,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,01</t>
+          <t>4,17; 7,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,04</t>
+          <t>1,74; 3,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,43</t>
+          <t>0,73; 2,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,43</t>
+          <t>3,5; 6,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,31</t>
+          <t>4,41; 7,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,33</t>
+          <t>1,76; 3,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,96</t>
+          <t>1,43; 2,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,01</t>
+          <t>3,79; 5,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,69</t>
+          <t>4,58; 6,72</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>617; 5564</t>
+          <t>608; 5543</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>882; 7615</t>
+          <t>745; 7433</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1951; 8911</t>
+          <t>1966; 9142</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2718; 10128</t>
+          <t>2669; 10356</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1394; 8179</t>
+          <t>1432; 8001</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>702; 6539</t>
+          <t>831; 7409</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1475; 8353</t>
+          <t>1510; 8714</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2105; 9738</t>
+          <t>1977; 9546</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2721; 11643</t>
+          <t>2920; 10818</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2468; 11483</t>
+          <t>2985; 12034</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4928; 14700</t>
+          <t>4823; 14223</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5829; 16710</t>
+          <t>6019; 17459</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1229; 6998</t>
+          <t>1239; 7460</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>622; 5187</t>
+          <t>619; 5186</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3458; 11103</t>
+          <t>3060; 10820</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4437; 14429</t>
+          <t>4546; 14870</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>679; 6458</t>
+          <t>618; 5909</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3251</t>
+          <t>0; 4242</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4703; 14586</t>
+          <t>4764; 13766</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8516; 21645</t>
+          <t>8682; 22137</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3069; 10924</t>
+          <t>2539; 10721</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>643; 6417</t>
+          <t>645; 5846</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9722; 22240</t>
+          <t>9978; 22006</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15588; 31891</t>
+          <t>15395; 31795</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>619; 5452</t>
+          <t>641; 6217</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1089; 6581</t>
+          <t>1116; 6994</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4018; 12190</t>
+          <t>4213; 12613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4798; 16476</t>
+          <t>4668; 16153</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2345; 9248</t>
+          <t>2320; 9430</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4476</t>
+          <t>433; 4777</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2465; 10082</t>
+          <t>2606; 10752</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7564; 20028</t>
+          <t>7402; 19302</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3999; 12268</t>
+          <t>3666; 12001</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2173; 9023</t>
+          <t>2161; 9606</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7955; 19376</t>
+          <t>8157; 19185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14733; 32796</t>
+          <t>14829; 30994</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>720; 6925</t>
+          <t>853; 6681</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2906; 10474</t>
+          <t>2911; 11326</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3858; 12649</t>
+          <t>3468; 13333</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7506; 18831</t>
+          <t>7107; 18818</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1302; 7419</t>
+          <t>1336; 8014</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>642; 5880</t>
+          <t>647; 5699</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4977; 15358</t>
+          <t>4906; 15228</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6796; 20920</t>
+          <t>7099; 20188</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3239; 11773</t>
+          <t>3290; 11014</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4431; 14015</t>
+          <t>4315; 13416</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10463; 24825</t>
+          <t>10297; 23746</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17376; 35538</t>
+          <t>17426; 34519</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6795; 17334</t>
+          <t>6303; 17237</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9022; 21847</t>
+          <t>8788; 22044</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18735; 35273</t>
+          <t>19551; 35676</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26948; 46707</t>
+          <t>27771; 47056</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8985; 21348</t>
+          <t>9182; 20637</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4017; 13079</t>
+          <t>3953; 12722</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19518; 36715</t>
+          <t>19984; 37235</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33070; 55711</t>
+          <t>33568; 56348</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17985; 34398</t>
+          <t>18112; 34993</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14645; 30019</t>
+          <t>14501; 30036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42709; 65880</t>
+          <t>41585; 65626</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65472; 95484</t>
+          <t>65345; 95924</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_ner_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2A_ner_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,32%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>5,13%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,27</t>
+          <t>1,23; 7,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,65</t>
+          <t>0,61; 5,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 10,15</t>
+          <t>1,42; 8,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 8,83</t>
+          <t>1,63; 7,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 6,76</t>
+          <t>0,58; 5,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,59</t>
+          <t>0,76; 8,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,33</t>
+          <t>2,11; 10,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,8</t>
+          <t>2,51; 9,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,84</t>
+          <t>1,29; 5,19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,74</t>
+          <t>1,38; 5,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,3</t>
+          <t>2,41; 7,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,78</t>
+          <t>2,51; 6,62</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,97</t>
+          <t>0,48; 4,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,02</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,12</t>
+          <t>2,64; 8,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,81</t>
+          <t>3,74; 9,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,2</t>
+          <t>0,99; 5,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,48; 3,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,85</t>
+          <t>2,21; 7,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 8,68</t>
+          <t>2,48; 7,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,03</t>
+          <t>1,18; 4,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,06</t>
+          <t>0,23; 2,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,72</t>
+          <t>3,09; 6,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,14</t>
+          <t>3,92; 8,13</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,91%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,53%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,76</t>
+          <t>1,99; 8,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,67</t>
+          <t>0,36; 4,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 10,82</t>
+          <t>2,01; 7,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 8,48</t>
+          <t>4,02; 10,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 8,38</t>
+          <t>0,57; 5,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,09</t>
+          <t>0,66; 6,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 8,09</t>
+          <t>3,54; 10,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 10,42</t>
+          <t>3,63; 10,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,44</t>
+          <t>1,65; 5,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,33</t>
+          <t>0,98; 3,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 7,69</t>
+          <t>3,33; 7,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,25</t>
+          <t>4,47; 9,02</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,1%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4,48%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,04</t>
+          <t>0,83; 4,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,76</t>
+          <t>0,42; 3,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,99</t>
+          <t>2,95; 9,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 11,2</t>
+          <t>4,0; 11,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,11</t>
+          <t>0,41; 4,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,68</t>
+          <t>1,98; 7,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 9,63</t>
+          <t>2,16; 7,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,92; 11,14</t>
+          <t>4,74; 12,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,42</t>
+          <t>1,02; 3,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,46</t>
+          <t>1,43; 4,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,31</t>
+          <t>3,42; 7,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,89</t>
+          <t>5,24; 10,61</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>5,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,42</t>
+          <t>1,76; 4,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,62</t>
+          <t>0,67; 2,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 6,79</t>
+          <t>3,51; 6,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,06</t>
+          <t>4,49; 7,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,9</t>
+          <t>1,37; 3,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,36</t>
+          <t>1,93; 4,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,52</t>
+          <t>3,68; 6,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,39</t>
+          <t>4,48; 7,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,39</t>
+          <t>1,77; 3,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,96</t>
+          <t>1,52; 3,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,99</t>
+          <t>3,95; 6,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,72</t>
+          <t>4,9; 7,21</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3743</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2868</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3985</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4597</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2443</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3228</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4625</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5548</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3743</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2868</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3985</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>5831</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10428</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>608; 5543</t>
+          <t>1458; 8276</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>745; 7433</t>
+          <t>683; 6679</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1966; 9142</t>
+          <t>1485; 9027</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2669; 10356</t>
+          <t>2048; 9866</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1432; 8001</t>
+          <t>615; 6107</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>831; 7409</t>
+          <t>735; 8016</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1510; 8714</t>
+          <t>1900; 9071</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1977; 9546</t>
+          <t>3035; 11003</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2920; 10818</t>
+          <t>2879; 11593</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2985; 12034</t>
+          <t>2896; 11422</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4823; 14223</t>
+          <t>4701; 14327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6019; 17459</t>
+          <t>6200; 16346</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2597</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8599</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14350</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3182</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1923</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6574</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8314</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2597</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8599</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14208</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22522</t>
+          <t>23093</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1239; 7460</t>
+          <t>678; 6386</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>619; 5186</t>
+          <t>0; 3234</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3060; 10820</t>
+          <t>4621; 14183</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4546; 14870</t>
+          <t>8861; 21409</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>618; 5909</t>
+          <t>1240; 6984</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4242</t>
+          <t>621; 5088</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4764; 13766</t>
+          <t>3360; 11703</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8682; 22137</t>
+          <t>4565; 14438</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2539; 10721</t>
+          <t>3130; 10905</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>645; 5846</t>
+          <t>638; 5816</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9978; 22006</t>
+          <t>10106; 21992</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15395; 31795</t>
+          <t>16523; 34264</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5423</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11159</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2465</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3053</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>7616</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9834</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4738</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1750</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5423</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>21097</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>641; 6217</t>
+          <t>2237; 9305</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1116; 6994</t>
+          <t>425; 4773</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4213; 12613</t>
+          <t>2664; 10125</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4668; 16153</t>
+          <t>6765; 18279</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2320; 9430</t>
+          <t>617; 5625</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>433; 4777</t>
+          <t>687; 6674</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2606; 10752</t>
+          <t>4123; 12676</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7402; 19302</t>
+          <t>5700; 16116</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3666; 12001</t>
+          <t>3638; 12254</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2161; 9606</t>
+          <t>2179; 8811</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8157; 19185</t>
+          <t>8315; 19161</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14829; 30994</t>
+          <t>14544; 29347</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9080</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12221</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2910</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5982</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>7474</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12366</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2135</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9080</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>25029</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>853; 6681</t>
+          <t>1297; 7508</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2911; 11326</t>
+          <t>644; 5828</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3468; 13333</t>
+          <t>4664; 14973</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7107; 18818</t>
+          <t>6782; 19625</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1336; 8014</t>
+          <t>677; 6884</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>647; 5699</t>
+          <t>2896; 11296</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4906; 15228</t>
+          <t>3603; 12711</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7099; 20188</t>
+          <t>7923; 20288</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3290; 11014</t>
+          <t>3282; 11279</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4315; 13416</t>
+          <t>4319; 14240</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10297; 23746</t>
+          <t>11115; 25572</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17426; 34519</t>
+          <t>17625; 35693</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>27087</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>42328</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>11000</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>14185</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>26289</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>36062</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>14449</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7400</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27087</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>37319</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79916</t>
+          <t>79646</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6303; 17237</t>
+          <t>9318; 21718</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8788; 22044</t>
+          <t>3583; 12897</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19551; 35676</t>
+          <t>20042; 36656</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27771; 47056</t>
+          <t>31498; 55840</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9182; 20637</t>
+          <t>6875; 17028</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3953; 12722</t>
+          <t>9196; 21670</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19984; 37235</t>
+          <t>19342; 35472</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33568; 56348</t>
+          <t>28185; 48112</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>18112; 34993</t>
+          <t>18219; 34190</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14501; 30036</t>
+          <t>15435; 30955</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41585; 65626</t>
+          <t>43336; 66358</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65345; 95924</t>
+          <t>65216; 95923</t>
         </is>
       </c>
     </row>
